--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">San Rosendo</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Alto Biobío</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tirúa</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:13</t>
+    <t xml:space="preserve">2026-10-04 08:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:53</t>
+    <t xml:space="preserve">2026-10-05 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -631,7 +631,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1144699.12</v>
+        <v>1144699.13</v>
       </c>
     </row>
     <row r="6">
@@ -750,7 +750,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1052858.62</v>
+        <v>1052858.63</v>
       </c>
     </row>
     <row r="13">
@@ -818,7 +818,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>983935.12</v>
+        <v>983935.13</v>
       </c>
     </row>
     <row r="17">
